--- a/JasonPlayground/gcp_medallion_learning_plan_jira_import.xlsx
+++ b/JasonPlayground/gcp_medallion_learning_plan_jira_import.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Ref8e75fc44734706"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start_Here" sheetId="2" r:id="R8f1be1e398804854"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epics_User_Stories" sheetId="3" r:id="R8bb5adcf1f954f55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed_Tasks" sheetId="4" r:id="R18a9e387d65641b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira_Import" sheetId="5" r:id="R0c5f957e9c0941ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="6" r:id="R6b1e9f2e38f6453b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task_2_Playbook" sheetId="7" r:id="R715cb42a117c4c24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dataset_Design" sheetId="8" r:id="R4b7f7c92509c415f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GCP_Objects" sheetId="9" r:id="Rfc5e8e6f89384623"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance_Checks" sheetId="10" r:id="R53e9fb27203e4e2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R044adcb08a504fb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start_Here" sheetId="2" r:id="R1899c44db1794176"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epics_User_Stories" sheetId="3" r:id="R5a8f9c73acd94423"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed_Tasks" sheetId="4" r:id="Ra2bd094781634423"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira_Import" sheetId="5" r:id="Ra713eee3b87d4b37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="6" r:id="R8f70eb992e664f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task_2_Playbook" sheetId="7" r:id="R288f0f5ded554c56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dataset_Design" sheetId="8" r:id="R325abef72fd2487b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GCP_Objects" sheetId="9" r:id="Rbf5e3336ed2f4005"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance_Checks" sheetId="10" r:id="R085fdaccd3344ef4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -159,7 +159,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Codex" id="{7826A91A-8800-49AF-BB3D-152BD15BCC48}"/>
+  <xltc:person displayName="Codex" id="{6C476D70-9A59-4C64-9AF2-0DC96135A930}"/>
 </xltc:personList>
 </file>
 
@@ -520,7 +520,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdff4ee3449724283"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0810e0d962984c03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -658,7 +658,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R877edf03fabd4766"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42257531887745ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -813,7 +813,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra572425944b042ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95c63f7720184c7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1053,7 +1053,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbabb1c7131734699"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f4e610f9b6344fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4691,7 +4691,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15461401774d4552"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R118016a6ef634548"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7455,7 +7455,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41a4abe61b394203"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2612c266592547d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7975,7 +7975,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d932965f7574b7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ea5d44beb3a4fa7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9088,7 +9088,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e39d736430a408e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57ee7d5819eb4433"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9328,7 +9328,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re085b78772a74522"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8640edb0b8a84e11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9483,7 +9483,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39449675120049ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2405e495076848a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>